--- a/examples/Ex.8_ElectreScore_mixed.xlsx
+++ b/examples/Ex.8_ElectreScore_mixed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentiunict-my.sharepoint.com/personal/zppsvn93e31c351c_studium_unict_it/Documents/PC/PhD/PAPERS/RULES Software X/Explainable-composite-indicator/examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{F8A5863D-D6C2-4BD5-87E9-96AA7489A2CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C27B2C0-B511-4A2D-8BC2-3DB765A58F49}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="8_{F8A5863D-D6C2-4BD5-87E9-96AA7489A2CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{517CCED3-D820-44F3-9A2B-6B9D28E6990B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D75860BD-C039-4F0C-90AA-C728D217AAAC}"/>
   </bookViews>
